--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,62 +767,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5326</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449177</t>
+          <t>449321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879050</t>
+          <t>879873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594912</t>
+          <t>594084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607566</t>
+          <t>607524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280118</t>
+          <t>1282164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294575</t>
+          <t>1294596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>673841</t>
+          <t>672726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680974</t>
+          <t>680976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>680631</t>
+          <t>679881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>698373</t>
+          <t>698107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1356834</t>
+          <t>1359214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1378010</t>
+          <t>1377712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>50163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65714</t>
+          <t>65876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590412</t>
+          <t>591772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608196</t>
+          <t>607290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566624</t>
+          <t>566036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>591033</t>
+          <t>592152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1165102</t>
+          <t>1164940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1194425</t>
+          <t>1194990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51574</t>
+          <t>50869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>82418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63521</t>
+          <t>65447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99289</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405383</t>
+          <t>406446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421070</t>
+          <t>421176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364674</t>
+          <t>365382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396226</t>
+          <t>396931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>777940</t>
+          <t>775750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>813708</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56071</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84119</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90081</t>
+          <t>92178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130167</t>
+          <t>130225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253715</t>
+          <t>254432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279061</t>
+          <t>279705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269877</t>
+          <t>270379</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300126</t>
+          <t>300622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>533615</t>
+          <t>533557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>573701</t>
+          <t>571604</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>37953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63213</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114831</t>
+          <t>113395</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152571</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161168</t>
+          <t>159519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207006</t>
+          <t>207014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186638</t>
+          <t>184362</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212014</t>
+          <t>211898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>236408</t>
+          <t>235988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274148</t>
+          <t>275584</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>431824</t>
+          <t>431816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477662</t>
+          <t>479311</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145479</t>
+          <t>147553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>293090</t>
+          <t>296365</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>366377</t>
+          <t>365898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>409542</t>
+          <t>410937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>495356</t>
+          <t>492949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3281300</t>
+          <t>3279226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3326902</t>
+          <t>3326871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3191932</t>
+          <t>3192411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3265219</t>
+          <t>3261944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6489732</t>
+          <t>6492139</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6575546</t>
+          <t>6574151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>959</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5775</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390949</t>
+          <t>390912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810403</t>
+          <t>809443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551204</t>
+          <t>550245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561274</t>
+          <t>561511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1141233</t>
+          <t>1141043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152106</t>
+          <t>1151691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>25990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660072</t>
+          <t>660537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639064</t>
+          <t>637736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653127</t>
+          <t>652901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303650</t>
+          <t>1304493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319770</t>
+          <t>1319918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27684</t>
+          <t>27385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51892</t>
+          <t>51300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>40379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69032</t>
+          <t>70149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>622340</t>
+          <t>622955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638352</t>
+          <t>638242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597185</t>
+          <t>597777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>621393</t>
+          <t>621692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1226093</t>
+          <t>1224976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1255616</t>
+          <t>1254746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58494</t>
+          <t>58712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92805</t>
+          <t>91067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>79805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122035</t>
+          <t>119098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441572</t>
+          <t>441542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462515</t>
+          <t>463126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404044</t>
+          <t>405782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438355</t>
+          <t>438137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>852732</t>
+          <t>855669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>894384</t>
+          <t>894962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63672</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95948</t>
+          <t>96629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82883</t>
+          <t>84144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>123311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>302906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319707</t>
+          <t>320556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>281814</t>
+          <t>281133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>314090</t>
+          <t>313898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>592905</t>
+          <t>588781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>629209</t>
+          <t>627948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53918</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>85410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124838</t>
+          <t>122609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124918</t>
+          <t>126212</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>170137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203080</t>
+          <t>199941</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224664</t>
+          <t>223122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>275331</t>
+          <t>277560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314743</t>
+          <t>314759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>486966</t>
+          <t>487030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532249</t>
+          <t>530955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85975</t>
+          <t>87899</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>127715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>281573</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>356245</t>
+          <t>358179</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>380773</t>
+          <t>382863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>462015</t>
+          <t>464351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3267103</t>
+          <t>3266635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3308375</t>
+          <t>3306451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3188297</t>
+          <t>3186363</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3262969</t>
+          <t>3259893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6476877</t>
+          <t>6474541</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6558119</t>
+          <t>6556029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295503</t>
+          <t>295021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311571</t>
+          <t>311529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695224</t>
+          <t>695766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711542</t>
+          <t>711603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415402</t>
+          <t>415084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489938</t>
+          <t>489153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505996</t>
+          <t>505638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911167</t>
+          <t>911019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927618</t>
+          <t>927147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27171</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29530</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509167</t>
+          <t>510006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526475</t>
+          <t>526464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>558425</t>
+          <t>558461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575987</t>
+          <t>575826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073198</t>
+          <t>1073845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1098810</t>
+          <t>1097831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59347</t>
+          <t>59337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68183</t>
+          <t>69142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104117</t>
+          <t>104223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72006</t>
+          <t>75462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155593</t>
+          <t>157339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828439</t>
+          <t>828449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871946</t>
+          <t>872121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608764</t>
+          <t>608658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644698</t>
+          <t>643739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1445074</t>
+          <t>1443328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1528661</t>
+          <t>1525205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37807</t>
+          <t>38160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62866</t>
+          <t>61842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85829</t>
+          <t>85655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111534</t>
+          <t>111684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128841</t>
+          <t>131118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166207</t>
+          <t>168736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498368</t>
+          <t>499392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523427</t>
+          <t>523074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>436371</t>
+          <t>436221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>462076</t>
+          <t>462250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>942932</t>
+          <t>940403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>980298</t>
+          <t>978021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58400</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>46679</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>158279</t>
+          <t>159381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84701</t>
+          <t>78920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197334</t>
+          <t>196155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>309765</t>
+          <t>309843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329272</t>
+          <t>330149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>450089</t>
+          <t>448987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>567494</t>
+          <t>561689</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>779199</t>
+          <t>780378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>891832</t>
+          <t>897613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66398</t>
+          <t>65343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89078</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174891</t>
+          <t>175496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203555</t>
+          <t>204494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248792</t>
+          <t>248671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286108</t>
+          <t>285532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193681</t>
+          <t>193990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>217416</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222276</t>
+          <t>221337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>250940</t>
+          <t>250335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>422482</t>
+          <t>423058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>459798</t>
+          <t>459919</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>178838</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261829</t>
+          <t>263678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>417804</t>
+          <t>413012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>567954</t>
+          <t>567137</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>652587</t>
+          <t>650438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>812477</t>
+          <t>818617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3197988</t>
+          <t>3196139</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3281223</t>
+          <t>3280979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3144326</t>
+          <t>3145143</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3294476</t>
+          <t>3299268</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6359620</t>
+          <t>6353480</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6519510</t>
+          <t>6521659</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_5-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_5-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449321</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879873</t>
+          <t>879546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594084</t>
+          <t>594872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607524</t>
+          <t>607372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1282164</t>
+          <t>1280878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294596</t>
+          <t>1294567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672726</t>
+          <t>672552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680976</t>
+          <t>680951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679881</t>
+          <t>680441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>698107</t>
+          <t>698980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1359214</t>
+          <t>1359191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1377712</t>
+          <t>1378131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>26076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50163</t>
+          <t>51178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65876</t>
+          <t>65365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591772</t>
+          <t>592022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607290</t>
+          <t>608068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566036</t>
+          <t>565021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>592152</t>
+          <t>590123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1164940</t>
+          <t>1165451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1194990</t>
+          <t>1195250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50869</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82418</t>
+          <t>82015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65447</t>
+          <t>64602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101479</t>
+          <t>99576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406446</t>
+          <t>405930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421176</t>
+          <t>421337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365382</t>
+          <t>365785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396931</t>
+          <t>396400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775750</t>
+          <t>777653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>811782</t>
+          <t>812627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>57048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53374</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>82668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92178</t>
+          <t>91015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130225</t>
+          <t>131983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254432</t>
+          <t>252738</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279705</t>
+          <t>280028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270379</t>
+          <t>271328</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300622</t>
+          <t>301226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>533557</t>
+          <t>531799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>571604</t>
+          <t>572767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65489</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113395</t>
+          <t>114178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152991</t>
+          <t>152218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159519</t>
+          <t>158123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207014</t>
+          <t>204742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184362</t>
+          <t>187417</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>211898</t>
+          <t>212988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>235988</t>
+          <t>236761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>275584</t>
+          <t>274801</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>431816</t>
+          <t>434088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>479311</t>
+          <t>480707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>101165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>149257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>297365</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>365898</t>
+          <t>371449</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>410937</t>
+          <t>412347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>492949</t>
+          <t>497420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3279226</t>
+          <t>3277522</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3326871</t>
+          <t>3325614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3192411</t>
+          <t>3186860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3261944</t>
+          <t>3260944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6492139</t>
+          <t>6487668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6574151</t>
+          <t>6572741</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390912</t>
+          <t>390769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809443</t>
+          <t>809510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>550245</t>
+          <t>550268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561511</t>
+          <t>560864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1141043</t>
+          <t>1141147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151691</t>
+          <t>1151763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,77 +4417,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14622</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8398</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23373</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>17084</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>10688</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14622</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8485</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23650</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>17084</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>10565</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>25990</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660537</t>
+          <t>661165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,82 +4525,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>646764</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>638013</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>652988</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1313399</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1302797</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1319795</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>98,72%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>646764</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>637736</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>652901</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1313399</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1304493</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1319918</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>23686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51300</t>
+          <t>51787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40379</t>
+          <t>40524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70149</t>
+          <t>68219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>622955</t>
+          <t>622362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638242</t>
+          <t>638032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597777</t>
+          <t>597290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>621692</t>
+          <t>621926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1224976</t>
+          <t>1226906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1254746</t>
+          <t>1254601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58712</t>
+          <t>59017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91067</t>
+          <t>91530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79805</t>
+          <t>78882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119098</t>
+          <t>119925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441542</t>
+          <t>442002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463126</t>
+          <t>463268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>405782</t>
+          <t>405319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438137</t>
+          <t>437832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855669</t>
+          <t>854842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>894962</t>
+          <t>895885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>33862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63864</t>
+          <t>62549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96629</t>
+          <t>96711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84144</t>
+          <t>82673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123311</t>
+          <t>120230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302906</t>
+          <t>300468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>320556</t>
+          <t>320259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>281133</t>
+          <t>281051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313898</t>
+          <t>315213</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>588781</t>
+          <t>591862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>627948</t>
+          <t>629419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57057</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85410</t>
+          <t>83861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122609</t>
+          <t>124006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126212</t>
+          <t>126479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170137</t>
+          <t>172265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199941</t>
+          <t>201830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>223122</t>
+          <t>223461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277560</t>
+          <t>276163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314759</t>
+          <t>316308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487030</t>
+          <t>484902</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>530955</t>
+          <t>530688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87899</t>
+          <t>85097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127715</t>
+          <t>129311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>284649</t>
+          <t>281670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>358179</t>
+          <t>355091</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>382863</t>
+          <t>383156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>464351</t>
+          <t>466397</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3266635</t>
+          <t>3265039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3306451</t>
+          <t>3309253</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3186363</t>
+          <t>3189451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3259893</t>
+          <t>3262872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6474541</t>
+          <t>6472495</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6556029</t>
+          <t>6555736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,32 +6755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306830</t>
+          <t>355812</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295021</t>
+          <t>343669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311529</t>
+          <t>360465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6868,32 +6868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>706817</t>
+          <t>763605</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695766</t>
+          <t>752663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711603</t>
+          <t>768268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -7141,27 +7141,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421150</t>
+          <t>474324</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415084</t>
+          <t>467482</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>499288</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489153</t>
+          <t>479316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505638</t>
+          <t>493694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>920437</t>
+          <t>961925</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911019</t>
+          <t>952089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927147</t>
+          <t>968730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,67 +7371,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>28684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27954</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19312</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37055</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>24180</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>16176</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33541</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>45592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30509</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>59019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -7484,69 +7484,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>519721</t>
+          <t>603198</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510006</t>
+          <t>592153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526464</t>
+          <t>610851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>595239</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>586138</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>603881</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>96,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>567822</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>558461</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>575826</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,33%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1341</t>
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1087542</t>
+          <t>1198437</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073845</t>
+          <t>1185010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1097831</t>
+          <t>1210256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37920</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59337</t>
+          <t>55120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85433</t>
+          <t>85972</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69142</t>
+          <t>73426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104223</t>
+          <t>100932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>126058</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75462</t>
+          <t>107876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157339</t>
+          <t>146253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>849866</t>
+          <t>660531</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828449</t>
+          <t>645497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872121</t>
+          <t>671522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>627448</t>
+          <t>650914</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608658</t>
+          <t>635954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643739</t>
+          <t>663460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1477314</t>
+          <t>1311446</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1443328</t>
+          <t>1291251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1525205</t>
+          <t>1329628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49327</t>
+          <t>52449</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>40913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61842</t>
+          <t>66622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>108007</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85655</t>
+          <t>93154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111684</t>
+          <t>123383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147156</t>
+          <t>160456</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131118</t>
+          <t>141566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168736</t>
+          <t>181060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>511907</t>
+          <t>556897</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499392</t>
+          <t>542724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523074</t>
+          <t>568433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>450077</t>
+          <t>500848</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>436221</t>
+          <t>485472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>462250</t>
+          <t>515701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>961983</t>
+          <t>1057746</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>940403</t>
+          <t>1037142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>978021</t>
+          <t>1076636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47468</t>
+          <t>49488</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58322</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>101504</t>
+          <t>112134</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>99688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159381</t>
+          <t>127011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>148972</t>
+          <t>161621</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78920</t>
+          <t>144711</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196155</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>320697</t>
+          <t>357592</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>309843</t>
+          <t>346627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330149</t>
+          <t>368037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>506864</t>
+          <t>327032</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>448987</t>
+          <t>312155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561689</t>
+          <t>339478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>827561</t>
+          <t>684625</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>780378</t>
+          <t>667234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>897613</t>
+          <t>701535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>76801</t>
+          <t>84473</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>72076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88769</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>189473</t>
+          <t>206769</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175496</t>
+          <t>190145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204494</t>
+          <t>222307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>266274</t>
+          <t>291242</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248671</t>
+          <t>270078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285532</t>
+          <t>312583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>205958</t>
+          <t>225725</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193990</t>
+          <t>212455</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217416</t>
+          <t>238122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>236358</t>
+          <t>257840</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>221337</t>
+          <t>242302</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>250335</t>
+          <t>274464</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>442316</t>
+          <t>483565</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>423058</t>
+          <t>462224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>459919</t>
+          <t>504729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>230531</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178838</t>
+          <t>219051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>263678</t>
+          <t>273162</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>517594</t>
+          <t>561666</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>413012</t>
+          <t>526629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>567137</t>
+          <t>597294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>748125</t>
+          <t>808367</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>650438</t>
+          <t>762491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>818617</t>
+          <t>855960</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3229286</t>
+          <t>3286061</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3196139</t>
+          <t>3259600</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3280979</t>
+          <t>3313711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3194686</t>
+          <t>3175288</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3145143</t>
+          <t>3139660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3299268</t>
+          <t>3210325</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6423972</t>
+          <t>6461349</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6353480</t>
+          <t>6413756</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6521659</t>
+          <t>6507225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
